--- a/artfynd/A 35550-2025 artfynd.xlsx
+++ b/artfynd/A 35550-2025 artfynd.xlsx
@@ -1128,7 +1128,7 @@
         <v>137404082</v>
       </c>
       <c r="B6" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137404083</v>
       </c>
       <c r="B7" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35550-2025 artfynd.xlsx
+++ b/artfynd/A 35550-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137404076</v>
       </c>
       <c r="B2" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137404079</v>
       </c>
       <c r="B3" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137404081</v>
       </c>
       <c r="B4" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137404077</v>
       </c>
       <c r="B5" t="n">
-        <v>87644</v>
+        <v>87655</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137404082</v>
       </c>
       <c r="B6" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137404083</v>
       </c>
       <c r="B7" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>137404078</v>
       </c>
       <c r="B8" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35550-2025 artfynd.xlsx
+++ b/artfynd/A 35550-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137404076</v>
       </c>
       <c r="B2" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137404079</v>
       </c>
       <c r="B3" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137404081</v>
       </c>
       <c r="B4" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137404077</v>
       </c>
       <c r="B5" t="n">
-        <v>87655</v>
+        <v>87656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137404082</v>
       </c>
       <c r="B6" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137404083</v>
       </c>
       <c r="B7" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>137404078</v>
       </c>
       <c r="B8" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35550-2025 artfynd.xlsx
+++ b/artfynd/A 35550-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137404076</v>
       </c>
       <c r="B2" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137404079</v>
       </c>
       <c r="B3" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137404081</v>
       </c>
       <c r="B4" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137404077</v>
       </c>
       <c r="B5" t="n">
-        <v>87656</v>
+        <v>87659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137404082</v>
       </c>
       <c r="B6" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137404083</v>
       </c>
       <c r="B7" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>137404078</v>
       </c>
       <c r="B8" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35550-2025 artfynd.xlsx
+++ b/artfynd/A 35550-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137404076</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137404079</v>
       </c>
       <c r="B3" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137404081</v>
       </c>
       <c r="B4" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137404077</v>
       </c>
       <c r="B5" t="n">
-        <v>87659</v>
+        <v>87663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137404082</v>
       </c>
       <c r="B6" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>137404083</v>
       </c>
       <c r="B7" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>137404078</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
